--- a/hall/resources/sample/ActivePass.xlsx
+++ b/hall/resources/sample/ActivePass.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -138,7 +138,7 @@
     <t>活跃通行证2期</t>
   </si>
   <si>
-    <t>2026/11/1 00:00:00</t>
+    <t>2026/11/01 00:00:00</t>
   </si>
   <si>
     <t>2026/11/21 23:59:59</t>
@@ -378,12 +378,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/ActivePass.xlsx
+++ b/hall/resources/sample/ActivePass.xlsx
@@ -159,43 +159,43 @@
     <t>2027/01/01 00:00:00</t>
   </si>
   <si>
-    <t>2026/01/21 23:59:59</t>
+    <t>2027/01/21 23:59:59</t>
   </si>
   <si>
     <t>活跃通行证5期</t>
   </si>
   <si>
-    <t>2026/02/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2026/02/21 23:59:59</t>
+    <t>2027/02/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2027/02/21 23:59:59</t>
   </si>
   <si>
     <t>活跃通行证6期</t>
   </si>
   <si>
-    <t>2026/03/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2026/03/21 23:59:59</t>
+    <t>2027/03/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2027/03/21 23:59:59</t>
   </si>
   <si>
     <t>活跃通行证7期</t>
   </si>
   <si>
-    <t>2026/04/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2026/04/21 23:59:59</t>
+    <t>2027/04/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2027/04/21 23:59:59</t>
   </si>
   <si>
     <t>活跃通行证8期</t>
   </si>
   <si>
-    <t>2025/05/01 00:00:00</t>
-  </si>
-  <si>
-    <t>2026/05/21 23:59:59</t>
+    <t>2027/05/01 00:00:00</t>
+  </si>
+  <si>
+    <t>2027/05/21 23:59:59</t>
   </si>
 </sst>
 </file>
